--- a/pagina/data/informe_mujeres.xlsx
+++ b/pagina/data/informe_mujeres.xlsx
@@ -42,6 +42,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -52,9 +55,6 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
@@ -75,13 +75,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -103,21 +109,21 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Centro Emergencia Mujer y Familia · Enero - Julio 2026 (preliminar)</t>
+          <t>Centro Emergencia Mujer y Familia · Enero - Agosto 2026 (preliminar)</t>
         </is>
       </c>
     </row>
@@ -511,7 +517,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>86663</v>
+        <v>99882</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +528,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-18 10:33</t>
+          <t>2026-09-18 09:54</t>
         </is>
       </c>
     </row>
@@ -584,10 +590,10 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>55934</v>
+        <v>64288</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -602,10 +608,10 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>25554</v>
+        <v>29579</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="4">
@@ -620,7 +626,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>5175</v>
+        <v>6015</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>6</v>
@@ -638,7 +644,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>73943</v>
+        <v>85232</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>85.3</v>
@@ -656,10 +662,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>10314</v>
+        <v>11835</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="7">
@@ -674,10 +680,10 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1415</v>
+        <v>1653</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -692,10 +698,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>991</v>
+        <v>1162</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -710,10 +716,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>44399</v>
+        <v>51190</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="10">
@@ -728,7 +734,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>27538</v>
+        <v>31769</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>31.8</v>
@@ -746,10 +752,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>14726</v>
+        <v>16923</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="12">
@@ -764,10 +770,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>45884</v>
+        <v>52617</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +788,10 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>29694</v>
+        <v>34374</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="14">
@@ -800,10 +806,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>11085</v>
+        <v>12891</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15">
@@ -818,7 +824,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>36228</v>
+        <v>41760</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>41.8</v>
@@ -836,10 +842,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>32670</v>
+        <v>37506</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="17">
@@ -854,10 +860,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>17468</v>
+        <v>20258</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="18">
@@ -872,10 +878,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>297</v>
+        <v>358</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19">
@@ -890,10 +896,10 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>77540</v>
+        <v>89312</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -908,10 +914,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>9123</v>
+        <v>10570</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="21">
@@ -926,10 +932,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>75655</v>
+        <v>87059</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>87.3</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="22">
@@ -944,7 +950,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>5711</v>
+        <v>6608</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>6.6</v>
@@ -962,10 +968,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>3611</v>
+        <v>4252</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="24">
@@ -980,10 +986,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1686</v>
+        <v>1963</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -998,7 +1004,7 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>1739</v>
+        <v>2013</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>2</v>
@@ -1016,7 +1022,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>10593</v>
+        <v>12140</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>12.2</v>
@@ -1034,10 +1040,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>47678</v>
+        <v>54804</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="28">
@@ -1052,7 +1058,7 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>19455</v>
+        <v>22406</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>22.4</v>
@@ -1088,7 +1094,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>0.1</v>
@@ -1106,10 +1112,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>5837</v>
+        <v>6822</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="32">
@@ -1124,10 +1130,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>18037</v>
+        <v>20709</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="33">
@@ -1142,7 +1148,7 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>40079</v>
+        <v>46127</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>46.2</v>
@@ -1160,10 +1166,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>22553</v>
+        <v>26044</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="35">
@@ -1178,7 +1184,7 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D35" s="9" t="n">
         <v>0</v>
@@ -1196,7 +1202,7 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>0.2</v>
@@ -1214,10 +1220,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>64367</v>
+        <v>74136</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="38">
@@ -1232,10 +1238,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>7092</v>
+        <v>8103</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="39">
@@ -1250,10 +1256,10 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>1499</v>
+        <v>1814</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="40">
@@ -1268,7 +1274,7 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>1375</v>
+        <v>1574</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>1.6</v>
@@ -1286,7 +1292,7 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>1049</v>
+        <v>1195</v>
       </c>
       <c r="D41" s="9" t="n">
         <v>1.2</v>
@@ -1304,7 +1310,7 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>490</v>
+        <v>567</v>
       </c>
       <c r="D42" s="9" t="n">
         <v>0.6</v>
@@ -1322,7 +1328,7 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D43" s="9" t="n">
         <v>0.2</v>
@@ -1376,7 +1382,7 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>29957</v>
+        <v>34570</v>
       </c>
       <c r="D46" s="9" t="n">
         <v>34.6</v>
@@ -1394,7 +1400,7 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>16483</v>
+        <v>18980</v>
       </c>
       <c r="D47" s="9" t="n">
         <v>19</v>
@@ -1412,7 +1418,7 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>12270</v>
+        <v>14153</v>
       </c>
       <c r="D48" s="9" t="n">
         <v>14.2</v>
@@ -1430,10 +1436,10 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>10634</v>
+        <v>12217</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="50">
@@ -1448,7 +1454,7 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>6874</v>
+        <v>7847</v>
       </c>
       <c r="D50" s="9" t="n">
         <v>7.9</v>
@@ -1466,7 +1472,7 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>4885</v>
+        <v>5601</v>
       </c>
       <c r="D51" s="9" t="n">
         <v>5.6</v>
@@ -1484,7 +1490,7 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>2042</v>
+        <v>2362</v>
       </c>
       <c r="D52" s="9" t="n">
         <v>2.4</v>
@@ -1502,7 +1508,7 @@
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>1225</v>
+        <v>1419</v>
       </c>
       <c r="D53" s="9" t="n">
         <v>1.4</v>
@@ -1516,14 +1522,14 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Lugar desolado</t>
+          <t>Centro de estudios de la persona usuaria</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>894</v>
+        <v>1070</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="55">
@@ -1534,14 +1540,14 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Centro de estudios de la persona usuaria</t>
+          <t>Lugar desolado</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>873</v>
+        <v>1054</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="56">
@@ -1556,7 +1562,7 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>526</v>
+        <v>609</v>
       </c>
       <c r="D56" s="9" t="n">
         <v>0.6</v>
@@ -1574,7 +1580,7 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>69290</v>
+        <v>79875</v>
       </c>
       <c r="D57" s="9" t="n">
         <v>80</v>
@@ -1592,7 +1598,7 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>17366</v>
+        <v>19998</v>
       </c>
       <c r="D58" s="9" t="n">
         <v>20</v>
@@ -1610,7 +1616,7 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D59" s="9" t="n">
         <v>0</v>
@@ -1671,7 +1677,7 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>2318</v>
+        <v>2662</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>2.7</v>
@@ -1689,7 +1695,7 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>1589</v>
+        <v>1799</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>1.8</v>
@@ -1707,10 +1713,10 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>33671</v>
+        <v>38684</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="5">
@@ -1725,10 +1731,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>62592</v>
+        <v>71856</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>72.2</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1743,10 +1749,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>736</v>
+        <v>851</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -1761,7 +1767,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>0.4</v>
@@ -1779,7 +1785,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>0.1</v>
@@ -1797,7 +1803,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>0.3</v>
@@ -1815,7 +1821,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>7170</v>
+        <v>8263</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>8.300000000000001</v>
@@ -1833,7 +1839,7 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>854</v>
+        <v>966</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>1</v>
@@ -1851,7 +1857,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>0.3</v>
@@ -1869,7 +1875,7 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>0.3</v>
@@ -1887,7 +1893,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>0.3</v>
@@ -1905,7 +1911,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>713</v>
+        <v>837</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>0.8</v>
@@ -1923,7 +1929,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>66944</v>
+        <v>77150</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>77.2</v>
@@ -1941,7 +1947,7 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>14795</v>
+        <v>17083</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>17.1</v>
@@ -1959,7 +1965,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>1142</v>
+        <v>1345</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>1.3</v>
@@ -1977,7 +1983,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>765</v>
+        <v>879</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>0.9</v>
@@ -1995,10 +2001,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2920</v>
+        <v>3340</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
@@ -2013,10 +2019,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>77246</v>
+        <v>89108</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="22">
@@ -2031,10 +2037,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>12699</v>
+        <v>14757</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="23">
@@ -2049,7 +2055,7 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1519</v>
+        <v>1786</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>1.8</v>
@@ -2067,7 +2073,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>33481</v>
+        <v>38595</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>38.6</v>
@@ -2085,7 +2091,7 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>69337</v>
+        <v>79935</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>80</v>
@@ -2103,10 +2109,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>721</v>
+        <v>863</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +2191,7 @@
         <v>2026</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>86663</v>
+        <v>99882</v>
       </c>
     </row>
   </sheetData>
@@ -2243,10 +2249,10 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>23785</v>
+        <v>27424</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="3">
@@ -2261,7 +2267,7 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>7543</v>
+        <v>8739</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>8.699999999999999</v>
@@ -2279,7 +2285,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>5422</v>
+        <v>6256</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>6.3</v>
@@ -2297,10 +2303,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>4419</v>
+        <v>5239</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="6">
@@ -2315,10 +2321,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>4015</v>
+        <v>4657</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -2333,7 +2339,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>3856</v>
+        <v>4402</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>4.4</v>
@@ -2351,10 +2357,10 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>3433</v>
+        <v>3923</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9">
@@ -2369,10 +2375,10 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>3382</v>
+        <v>3824</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
@@ -2387,7 +2393,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3306</v>
+        <v>3818</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>3.8</v>
@@ -2405,7 +2411,7 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>3088</v>
+        <v>3596</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>3.6</v>
@@ -2423,7 +2429,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>2899</v>
+        <v>3322</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>3.3</v>
@@ -2437,11 +2443,11 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>CALLAO</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>2436</v>
+        <v>2827</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>2.8</v>
@@ -2455,11 +2461,11 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>LAMBAYEQUE</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2432</v>
+        <v>2765</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>2.8</v>
@@ -2477,10 +2483,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>2390</v>
+        <v>2740</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -2495,7 +2501,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2313</v>
+        <v>2658</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>2.7</v>
@@ -2509,11 +2515,11 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1633</v>
+        <v>1894</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1.9</v>
@@ -2527,14 +2533,14 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>1629</v>
+        <v>1839</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19">
@@ -2549,10 +2555,10 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>1518</v>
+        <v>1741</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="20">
@@ -2567,7 +2573,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1410</v>
+        <v>1629</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>1.6</v>
@@ -2585,7 +2591,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1300</v>
+        <v>1487</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>1.5</v>
@@ -2603,7 +2609,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1116</v>
+        <v>1271</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>1.3</v>
@@ -2621,7 +2627,7 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1066</v>
+        <v>1217</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>1.2</v>
@@ -2639,7 +2645,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>838</v>
+        <v>956</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>1</v>
@@ -2657,7 +2663,7 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>723</v>
+        <v>830</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>0.8</v>
@@ -2675,7 +2681,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>711</v>
+        <v>828</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>0.8</v>
@@ -2693,7 +2699,7 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>19695</v>
+        <v>22718</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>22.7</v>
@@ -2711,7 +2717,7 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>7543</v>
+        <v>8739</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>8.699999999999999</v>
@@ -2729,7 +2735,7 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>5422</v>
+        <v>6256</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>6.3</v>
@@ -2747,10 +2753,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4419</v>
+        <v>5239</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="31">
@@ -2765,7 +2771,7 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>4090</v>
+        <v>4706</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>4.7</v>
@@ -2783,10 +2789,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>4015</v>
+        <v>4657</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="33">
@@ -2801,7 +2807,7 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>3856</v>
+        <v>4402</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>4.4</v>
@@ -2819,10 +2825,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>3433</v>
+        <v>3923</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="35">
@@ -2837,10 +2843,10 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>3382</v>
+        <v>3824</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="36">
@@ -2855,7 +2861,7 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>3306</v>
+        <v>3818</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>3.8</v>
@@ -2873,7 +2879,7 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>3088</v>
+        <v>3596</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>3.6</v>
@@ -2891,7 +2897,7 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>2899</v>
+        <v>3322</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>3.3</v>
@@ -2905,11 +2911,11 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>CALLAO</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>2436</v>
+        <v>2827</v>
       </c>
       <c r="D39" s="9" t="n">
         <v>2.8</v>
@@ -2923,11 +2929,11 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>LAMBAYEQUE</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>2432</v>
+        <v>2765</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>2.8</v>
@@ -2945,10 +2951,10 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>2390</v>
+        <v>2740</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="42">
@@ -2963,7 +2969,7 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>2313</v>
+        <v>2658</v>
       </c>
       <c r="D42" s="9" t="n">
         <v>2.7</v>
@@ -2977,11 +2983,11 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>1633</v>
+        <v>1894</v>
       </c>
       <c r="D43" s="9" t="n">
         <v>1.9</v>
@@ -2995,14 +3001,14 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>1629</v>
+        <v>1839</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="45">
@@ -3017,10 +3023,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>1518</v>
+        <v>1741</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="46">
@@ -3035,7 +3041,7 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>1410</v>
+        <v>1629</v>
       </c>
       <c r="D46" s="9" t="n">
         <v>1.6</v>
@@ -3053,7 +3059,7 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>1300</v>
+        <v>1487</v>
       </c>
       <c r="D47" s="9" t="n">
         <v>1.5</v>
@@ -3071,7 +3077,7 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>1116</v>
+        <v>1271</v>
       </c>
       <c r="D48" s="9" t="n">
         <v>1.3</v>
@@ -3089,7 +3095,7 @@
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>1066</v>
+        <v>1217</v>
       </c>
       <c r="D49" s="9" t="n">
         <v>1.2</v>
@@ -3107,7 +3113,7 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>838</v>
+        <v>956</v>
       </c>
       <c r="D50" s="9" t="n">
         <v>1</v>
@@ -3125,7 +3131,7 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>723</v>
+        <v>830</v>
       </c>
       <c r="D51" s="9" t="n">
         <v>0.8</v>
@@ -3143,7 +3149,7 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>711</v>
+        <v>828</v>
       </c>
       <c r="D52" s="9" t="n">
         <v>0.8</v>
@@ -3220,10 +3226,10 @@
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>39813</v>
+        <v>46122</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="3">
@@ -3242,7 +3248,7 @@
         </is>
       </c>
       <c r="E3" s="8" t="n">
-        <v>20554</v>
+        <v>23677</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>23.7</v>
@@ -3264,10 +3270,10 @@
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>19690</v>
+        <v>22583</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="5">
@@ -3286,10 +3292,10 @@
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>18137</v>
+        <v>20796</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="6">
@@ -3308,10 +3314,10 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>17381</v>
+        <v>19949</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -3330,7 +3336,7 @@
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>9967</v>
+        <v>11488</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>11.5</v>
@@ -3352,10 +3358,10 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>9848</v>
+        <v>11267</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="9">
@@ -3374,10 +3380,10 @@
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>6562</v>
+        <v>7513</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
@@ -3396,7 +3402,7 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>57281</v>
+        <v>66043</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>66.09999999999999</v>
@@ -3418,7 +3424,7 @@
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>24898</v>
+        <v>28641</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>28.7</v>
@@ -3440,7 +3446,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>19255</v>
+        <v>22190</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>22.2</v>
@@ -3462,10 +3468,10 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>17580</v>
+        <v>20105</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="14">
@@ -3484,10 +3490,10 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>16108</v>
+        <v>18371</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="15">
@@ -3506,10 +3512,10 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>13706</v>
+        <v>15705</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="16">
@@ -3528,10 +3534,10 @@
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>13288</v>
+        <v>15336</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="17">
@@ -3550,10 +3556,10 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>10954</v>
+        <v>12484</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
@@ -3576,10 +3582,10 @@
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1185</v>
+        <v>1345</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
@@ -3602,10 +3608,10 @@
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>910</v>
+        <v>1042</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3628,7 +3634,7 @@
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>724</v>
+        <v>803</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.8</v>
@@ -3654,7 +3660,7 @@
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>577</v>
+        <v>653</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>0.7</v>
@@ -3680,7 +3686,7 @@
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>466</v>
+        <v>537</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.5</v>
@@ -3706,7 +3712,7 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>407</v>
+        <v>453</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.5</v>
@@ -3732,10 +3738,10 @@
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>55070</v>
+        <v>63241</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>63.5</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="25">
@@ -3758,10 +3764,10 @@
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>33052</v>
+        <v>37936</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -3784,7 +3790,7 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>9659</v>
+        <v>11107</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>11.1</v>
@@ -3810,10 +3816,10 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>6839</v>
+        <v>7821</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="28">
@@ -3836,7 +3842,7 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>6320</v>
+        <v>7329</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>7.3</v>
@@ -3862,7 +3868,7 @@
         </is>
       </c>
       <c r="E29" s="8" t="n">
-        <v>6277</v>
+        <v>7198</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>7.2</v>
@@ -3888,10 +3894,10 @@
         </is>
       </c>
       <c r="E30" s="8" t="n">
-        <v>12365</v>
+        <v>14108</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="31">
@@ -3914,7 +3920,7 @@
         </is>
       </c>
       <c r="E31" s="8" t="n">
-        <v>7816</v>
+        <v>8972</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>9</v>
@@ -3940,10 +3946,10 @@
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>7250</v>
+        <v>8292</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3966,7 +3972,7 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>5593</v>
+        <v>6483</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>6.5</v>
@@ -3992,10 +3998,10 @@
         </is>
       </c>
       <c r="E34" s="8" t="n">
-        <v>3091</v>
+        <v>3507</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="35">
@@ -4018,10 +4024,10 @@
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>2680</v>
+        <v>3039</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -4044,7 +4050,7 @@
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>7170</v>
+        <v>8263</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>8.300000000000001</v>
@@ -4070,10 +4076,10 @@
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>4420</v>
+        <v>5167</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="38">
@@ -4096,7 +4102,7 @@
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>2922</v>
+        <v>3406</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>3.4</v>
@@ -4122,7 +4128,7 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1199</v>
+        <v>1390</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>1.4</v>
@@ -4148,7 +4154,7 @@
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.5</v>
@@ -4174,7 +4180,7 @@
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.4</v>
@@ -4246,10 +4252,10 @@
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>667</v>
+        <v>768</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>51.3</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="3">
@@ -4269,10 +4275,10 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>543</v>
+        <v>616</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="4">
@@ -4292,7 +4298,7 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>6.9</v>
@@ -4315,7 +4321,7 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1189</v>
+        <v>1360</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>91.5</v>
@@ -4338,10 +4344,10 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -4361,10 +4367,10 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
@@ -4407,10 +4413,10 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>694</v>
+        <v>793</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="10">
@@ -4430,10 +4436,10 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>509</v>
+        <v>586</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="11">
@@ -4453,10 +4459,10 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
@@ -4476,10 +4482,10 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>522</v>
+        <v>605</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="13">
@@ -4499,10 +4505,10 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>502</v>
+        <v>583</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="14">
@@ -4522,10 +4528,10 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>21.2</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="15">
@@ -4545,10 +4551,10 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>443</v>
+        <v>520</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>34.1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -4568,10 +4574,10 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>439</v>
+        <v>493</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>33.8</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="17">
@@ -4591,10 +4597,10 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="18">
@@ -4614,7 +4620,7 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0.5</v>
@@ -4637,10 +4643,10 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>2636</v>
+        <v>3002</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>68.40000000000001</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="20">
@@ -4660,10 +4666,10 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>955</v>
+        <v>1099</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -4683,10 +4689,10 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="22">
@@ -4706,10 +4712,10 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>3243</v>
+        <v>3705</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="23">
@@ -4729,10 +4735,10 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>492</v>
+        <v>555</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="24">
@@ -4752,7 +4758,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E24" s="9" t="n">
         <v>2.3</v>
@@ -4775,10 +4781,10 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
@@ -4798,10 +4804,10 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>1830</v>
+        <v>2094</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="27">
@@ -4821,10 +4827,10 @@
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>1504</v>
+        <v>1713</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="28">
@@ -4844,7 +4850,7 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>522</v>
+        <v>595</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>13.5</v>
@@ -4867,10 +4873,10 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>2084</v>
+        <v>2350</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>54</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="30">
@@ -4890,10 +4896,10 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>1374</v>
+        <v>1571</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="31">
@@ -4913,10 +4919,10 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>398</v>
+        <v>481</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="32">
@@ -4936,10 +4942,10 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>1784</v>
+        <v>2043</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="33">
@@ -4959,10 +4965,10 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>1519</v>
+        <v>1718</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34">
@@ -4982,10 +4988,10 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>521</v>
+        <v>609</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="35">
@@ -5008,7 +5014,7 @@
         <v>32</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="36">
@@ -5028,10 +5034,10 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1103</v>
+        <v>1263</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>72.7</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="37">
@@ -5051,10 +5057,10 @@
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="38">
@@ -5074,10 +5080,10 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -5097,10 +5103,10 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>1212</v>
+        <v>1387</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="40">
@@ -5120,10 +5126,10 @@
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="41">
@@ -5143,10 +5149,10 @@
         </is>
       </c>
       <c r="D41" s="8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="42">
@@ -5169,7 +5175,7 @@
         <v>9</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43">
@@ -5189,10 +5195,10 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>906</v>
+        <v>1035</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>59.7</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="44">
@@ -5212,10 +5218,10 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>358</v>
+        <v>417</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
@@ -5235,10 +5241,10 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="46">
@@ -5258,10 +5264,10 @@
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>962</v>
+        <v>1098</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>63.4</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="47">
@@ -5281,10 +5287,10 @@
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>411</v>
+        <v>473</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="48">
@@ -5304,10 +5310,10 @@
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -5327,10 +5333,10 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>674</v>
+        <v>790</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>44.4</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="50">
@@ -5350,10 +5356,10 @@
         </is>
       </c>
       <c r="D50" s="8" t="n">
-        <v>627</v>
+        <v>707</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>41.3</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="51">
@@ -5373,10 +5379,10 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="52">
@@ -5396,7 +5402,7 @@
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E52" s="9" t="n">
         <v>0.3</v>
@@ -5419,10 +5425,10 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>4737</v>
+        <v>5470</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>62.8</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="54">
@@ -5442,10 +5448,10 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>2256</v>
+        <v>2618</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -5465,10 +5471,10 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>550</v>
+        <v>651</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="56">
@@ -5488,10 +5494,10 @@
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>6125</v>
+        <v>7072</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -5511,10 +5517,10 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>1130</v>
+        <v>1325</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="58">
@@ -5534,10 +5540,10 @@
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -5557,7 +5563,7 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="E59" s="9" t="n">
         <v>1.9</v>
@@ -5580,10 +5586,10 @@
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>4531</v>
+        <v>5262</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>60.1</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="61">
@@ -5603,10 +5609,10 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>1720</v>
+        <v>1986</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="62">
@@ -5626,7 +5632,7 @@
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1292</v>
+        <v>1491</v>
       </c>
       <c r="E62" s="9" t="n">
         <v>17.1</v>
@@ -5649,10 +5655,10 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>3741</v>
+        <v>4315</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="64">
@@ -5672,10 +5678,10 @@
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>2935</v>
+        <v>3412</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65">
@@ -5695,10 +5701,10 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>867</v>
+        <v>1012</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="66">
@@ -5718,10 +5724,10 @@
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>3564</v>
+        <v>4137</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="67">
@@ -5741,10 +5747,10 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>2635</v>
+        <v>3043</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="68">
@@ -5764,10 +5770,10 @@
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>1316</v>
+        <v>1529</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="69">
@@ -5787,10 +5793,10 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="70">
@@ -5810,10 +5816,10 @@
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>2167</v>
+        <v>2529</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="71">
@@ -5833,10 +5839,10 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>767</v>
+        <v>894</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="72">
@@ -5856,10 +5862,10 @@
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="73">
@@ -5879,7 +5885,7 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>2648</v>
+        <v>3087</v>
       </c>
       <c r="E73" s="9" t="n">
         <v>85.8</v>
@@ -5902,7 +5908,7 @@
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="E74" s="9" t="n">
         <v>11.9</v>
@@ -5925,7 +5931,7 @@
         </is>
       </c>
       <c r="D75" s="8" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E75" s="9" t="n">
         <v>1.7</v>
@@ -5948,10 +5954,10 @@
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77">
@@ -5971,10 +5977,10 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>1549</v>
+        <v>1825</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="78">
@@ -5994,10 +6000,10 @@
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>1277</v>
+        <v>1480</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="79">
@@ -6017,10 +6023,10 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="80">
@@ -6040,10 +6046,10 @@
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>1943</v>
+        <v>2264</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81">
@@ -6063,10 +6069,10 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>839</v>
+        <v>955</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>27.2</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="82">
@@ -6086,10 +6092,10 @@
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>306</v>
+        <v>377</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="83">
@@ -6109,10 +6115,10 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>1373</v>
+        <v>1583</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>44.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84">
@@ -6132,10 +6138,10 @@
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>1247</v>
+        <v>1448</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="85">
@@ -6155,10 +6161,10 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>451</v>
+        <v>546</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="86">
@@ -6178,10 +6184,10 @@
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
@@ -6201,10 +6207,10 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>1520</v>
+        <v>1731</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>65.7</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -6224,10 +6230,10 @@
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>688</v>
+        <v>803</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="89">
@@ -6247,10 +6253,10 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="90">
@@ -6270,10 +6276,10 @@
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>2094</v>
+        <v>2411</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>90.5</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="91">
@@ -6293,10 +6299,10 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="92">
@@ -6316,10 +6322,10 @@
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="93">
@@ -6339,7 +6345,7 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E93" s="9" t="n">
         <v>0.4</v>
@@ -6362,10 +6368,10 @@
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>1052</v>
+        <v>1217</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="95">
@@ -6385,10 +6391,10 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>828</v>
+        <v>950</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="96">
@@ -6408,10 +6414,10 @@
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="97">
@@ -6431,10 +6437,10 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>1264</v>
+        <v>1442</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>54.6</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="98">
@@ -6454,10 +6460,10 @@
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>738</v>
+        <v>867</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>31.9</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="99">
@@ -6477,10 +6483,10 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="100">
@@ -6500,10 +6506,10 @@
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>948</v>
+        <v>1085</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="101">
@@ -6523,10 +6529,10 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>863</v>
+        <v>1003</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="102">
@@ -6546,10 +6552,10 @@
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>500</v>
+        <v>568</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="103">
@@ -6592,10 +6598,10 @@
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>1411</v>
+        <v>1671</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>58</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="105">
@@ -6615,10 +6621,10 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>763</v>
+        <v>852</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>31.4</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="106">
@@ -6638,10 +6644,10 @@
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="107">
@@ -6661,10 +6667,10 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>1909</v>
+        <v>2229</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="108">
@@ -6684,10 +6690,10 @@
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>383</v>
+        <v>441</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="109">
@@ -6707,10 +6713,10 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="110">
@@ -6730,10 +6736,10 @@
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="111">
@@ -6753,10 +6759,10 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>1285</v>
+        <v>1511</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="112">
@@ -6776,10 +6782,10 @@
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>619</v>
+        <v>714</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="113">
@@ -6799,10 +6805,10 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>528</v>
+        <v>602</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="114">
@@ -6818,14 +6824,14 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Vínculo relacional familiar</t>
+          <t>Vínculo relacional de pareja</t>
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>1105</v>
+        <v>1292</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="115">
@@ -6841,14 +6847,14 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Vínculo relacional de pareja</t>
+          <t>Vínculo relacional familiar</t>
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>1094</v>
+        <v>1269</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="116">
@@ -6868,10 +6874,10 @@
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="117">
@@ -6891,10 +6897,10 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>1270</v>
+        <v>1494</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>52.2</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="118">
@@ -6914,10 +6920,10 @@
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>734</v>
+        <v>845</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="119">
@@ -6937,10 +6943,10 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>417</v>
+        <v>475</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="120">
@@ -6960,7 +6966,7 @@
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E120" s="9" t="n">
         <v>0.5</v>
@@ -6983,7 +6989,7 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>3625</v>
+        <v>4186</v>
       </c>
       <c r="E121" s="9" t="n">
         <v>66.90000000000001</v>
@@ -7006,10 +7012,10 @@
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1468</v>
+        <v>1685</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="123">
@@ -7029,10 +7035,10 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>329</v>
+        <v>385</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="124">
@@ -7052,10 +7058,10 @@
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>4556</v>
+        <v>5259</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7075,7 +7081,7 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>696</v>
+        <v>799</v>
       </c>
       <c r="E125" s="9" t="n">
         <v>12.8</v>
@@ -7098,7 +7104,7 @@
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E126" s="9" t="n">
         <v>2.3</v>
@@ -7121,10 +7127,10 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="128">
@@ -7144,7 +7150,7 @@
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>3128</v>
+        <v>3612</v>
       </c>
       <c r="E128" s="9" t="n">
         <v>57.7</v>
@@ -7167,10 +7173,10 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1366</v>
+        <v>1569</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="130">
@@ -7190,10 +7196,10 @@
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>928</v>
+        <v>1075</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="131">
@@ -7213,10 +7219,10 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>2969</v>
+        <v>3422</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="132">
@@ -7236,10 +7242,10 @@
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>1815</v>
+        <v>2083</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="133">
@@ -7259,10 +7265,10 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>638</v>
+        <v>751</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134">
@@ -7282,10 +7288,10 @@
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>2511</v>
+        <v>2883</v>
       </c>
       <c r="E134" s="9" t="n">
-        <v>46.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="135">
@@ -7305,7 +7311,7 @@
         </is>
       </c>
       <c r="D135" s="8" t="n">
-        <v>1970</v>
+        <v>2272</v>
       </c>
       <c r="E135" s="9" t="n">
         <v>36.3</v>
@@ -7328,10 +7334,10 @@
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>927</v>
+        <v>1085</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="137">
@@ -7351,7 +7357,7 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E137" s="9" t="n">
         <v>0.3</v>
@@ -7374,10 +7380,10 @@
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>674</v>
+        <v>775</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>60.4</v>
+        <v>61</v>
       </c>
     </row>
     <row r="139">
@@ -7397,10 +7403,10 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>32.3</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="140">
@@ -7420,10 +7426,10 @@
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E140" s="9" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="141">
@@ -7443,10 +7449,10 @@
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>866</v>
+        <v>990</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>77.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -7466,10 +7472,10 @@
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="E142" s="9" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="143">
@@ -7489,7 +7495,7 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E143" s="9" t="n">
         <v>3.1</v>
@@ -7535,10 +7541,10 @@
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>494</v>
+        <v>572</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>44.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="146">
@@ -7558,10 +7564,10 @@
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>353</v>
+        <v>399</v>
       </c>
       <c r="E146" s="9" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="147">
@@ -7581,10 +7587,10 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="148">
@@ -7604,7 +7610,7 @@
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="E148" s="9" t="n">
         <v>50.1</v>
@@ -7627,10 +7633,10 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>415</v>
+        <v>471</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="150">
@@ -7650,10 +7656,10 @@
         </is>
       </c>
       <c r="D150" s="8" t="n">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="E150" s="9" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="151">
@@ -7673,7 +7679,7 @@
         </is>
       </c>
       <c r="D151" s="8" t="n">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="E151" s="9" t="n">
         <v>44.5</v>
@@ -7696,10 +7702,10 @@
         </is>
       </c>
       <c r="D152" s="8" t="n">
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="E152" s="9" t="n">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="153">
@@ -7719,10 +7725,10 @@
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="154">
@@ -7742,10 +7748,10 @@
         </is>
       </c>
       <c r="D154" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="155">
@@ -7765,10 +7771,10 @@
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>1813</v>
+        <v>2079</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="156">
@@ -7788,7 +7794,7 @@
         </is>
       </c>
       <c r="D156" s="8" t="n">
-        <v>964</v>
+        <v>1105</v>
       </c>
       <c r="E156" s="9" t="n">
         <v>33.3</v>
@@ -7811,7 +7817,7 @@
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E157" s="9" t="n">
         <v>4.2</v>
@@ -7834,10 +7840,10 @@
         </is>
       </c>
       <c r="D158" s="8" t="n">
-        <v>2593</v>
+        <v>2984</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>89.40000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="159">
@@ -7857,10 +7863,10 @@
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="160">
@@ -7880,7 +7886,7 @@
         </is>
       </c>
       <c r="D160" s="8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E160" s="9" t="n">
         <v>1.1</v>
@@ -7903,7 +7909,7 @@
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E161" s="9" t="n">
         <v>0.5</v>
@@ -7926,10 +7932,10 @@
         </is>
       </c>
       <c r="D162" s="8" t="n">
-        <v>1483</v>
+        <v>1709</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="163">
@@ -7949,10 +7955,10 @@
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>836</v>
+        <v>967</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="164">
@@ -7972,10 +7978,10 @@
         </is>
       </c>
       <c r="D164" s="8" t="n">
-        <v>580</v>
+        <v>646</v>
       </c>
       <c r="E164" s="9" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="165">
@@ -7995,10 +8001,10 @@
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>1556</v>
+        <v>1790</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="166">
@@ -8018,10 +8024,10 @@
         </is>
       </c>
       <c r="D166" s="8" t="n">
-        <v>862</v>
+        <v>996</v>
       </c>
       <c r="E166" s="9" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167">
@@ -8041,10 +8047,10 @@
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>481</v>
+        <v>536</v>
       </c>
       <c r="E167" s="9" t="n">
-        <v>16.6</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="168">
@@ -8064,10 +8070,10 @@
         </is>
       </c>
       <c r="D168" s="8" t="n">
-        <v>1099</v>
+        <v>1267</v>
       </c>
       <c r="E168" s="9" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="169">
@@ -8087,10 +8093,10 @@
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>1058</v>
+        <v>1217</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="170">
@@ -8110,10 +8116,10 @@
         </is>
       </c>
       <c r="D170" s="8" t="n">
-        <v>738</v>
+        <v>832</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>25.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="171">
@@ -8133,10 +8139,10 @@
         </is>
       </c>
       <c r="D171" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="172">
@@ -8156,10 +8162,10 @@
         </is>
       </c>
       <c r="D172" s="8" t="n">
-        <v>2287</v>
+        <v>2595</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>67.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -8179,10 +8185,10 @@
         </is>
       </c>
       <c r="D173" s="8" t="n">
-        <v>951</v>
+        <v>1069</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174">
@@ -8202,10 +8208,10 @@
         </is>
       </c>
       <c r="D174" s="8" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="175">
@@ -8225,10 +8231,10 @@
         </is>
       </c>
       <c r="D175" s="8" t="n">
-        <v>2823</v>
+        <v>3196</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -8248,7 +8254,7 @@
         </is>
       </c>
       <c r="D176" s="8" t="n">
-        <v>494</v>
+        <v>557</v>
       </c>
       <c r="E176" s="9" t="n">
         <v>14.6</v>
@@ -8271,7 +8277,7 @@
         </is>
       </c>
       <c r="D177" s="8" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E177" s="9" t="n">
         <v>1</v>
@@ -8294,7 +8300,7 @@
         </is>
       </c>
       <c r="D178" s="8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E178" s="9" t="n">
         <v>0.9</v>
@@ -8317,10 +8323,10 @@
         </is>
       </c>
       <c r="D179" s="8" t="n">
-        <v>1473</v>
+        <v>1664</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="180">
@@ -8340,10 +8346,10 @@
         </is>
       </c>
       <c r="D180" s="8" t="n">
-        <v>1301</v>
+        <v>1462</v>
       </c>
       <c r="E180" s="9" t="n">
-        <v>38.5</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="181">
@@ -8363,10 +8369,10 @@
         </is>
       </c>
       <c r="D181" s="8" t="n">
-        <v>608</v>
+        <v>698</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="182">
@@ -8386,10 +8392,10 @@
         </is>
       </c>
       <c r="D182" s="8" t="n">
-        <v>1966</v>
+        <v>2229</v>
       </c>
       <c r="E182" s="9" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="183">
@@ -8409,10 +8415,10 @@
         </is>
       </c>
       <c r="D183" s="8" t="n">
-        <v>1006</v>
+        <v>1131</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="184">
@@ -8432,7 +8438,7 @@
         </is>
       </c>
       <c r="D184" s="8" t="n">
-        <v>410</v>
+        <v>464</v>
       </c>
       <c r="E184" s="9" t="n">
         <v>12.1</v>
@@ -8455,10 +8461,10 @@
         </is>
       </c>
       <c r="D185" s="8" t="n">
-        <v>1438</v>
+        <v>1645</v>
       </c>
       <c r="E185" s="9" t="n">
-        <v>42.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="186">
@@ -8478,10 +8484,10 @@
         </is>
       </c>
       <c r="D186" s="8" t="n">
-        <v>1254</v>
+        <v>1409</v>
       </c>
       <c r="E186" s="9" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="187">
@@ -8501,10 +8507,10 @@
         </is>
       </c>
       <c r="D187" s="8" t="n">
-        <v>684</v>
+        <v>760</v>
       </c>
       <c r="E187" s="9" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="188">
@@ -8524,10 +8530,10 @@
         </is>
       </c>
       <c r="D188" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E188" s="9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="189">
@@ -8547,10 +8553,10 @@
         </is>
       </c>
       <c r="D189" s="8" t="n">
-        <v>2103</v>
+        <v>2391</v>
       </c>
       <c r="E189" s="9" t="n">
-        <v>61.3</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="190">
@@ -8570,10 +8576,10 @@
         </is>
       </c>
       <c r="D190" s="8" t="n">
-        <v>1113</v>
+        <v>1289</v>
       </c>
       <c r="E190" s="9" t="n">
-        <v>32.4</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="191">
@@ -8593,10 +8599,10 @@
         </is>
       </c>
       <c r="D191" s="8" t="n">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="E191" s="9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="192">
@@ -8616,10 +8622,10 @@
         </is>
       </c>
       <c r="D192" s="8" t="n">
-        <v>2949</v>
+        <v>3378</v>
       </c>
       <c r="E192" s="9" t="n">
-        <v>85.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="193">
@@ -8639,10 +8645,10 @@
         </is>
       </c>
       <c r="D193" s="8" t="n">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="E193" s="9" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="194">
@@ -8662,7 +8668,7 @@
         </is>
       </c>
       <c r="D194" s="8" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E194" s="9" t="n">
         <v>1.9</v>
@@ -8685,7 +8691,7 @@
         </is>
       </c>
       <c r="D195" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E195" s="9" t="n">
         <v>0.6</v>
@@ -8708,10 +8714,10 @@
         </is>
       </c>
       <c r="D196" s="8" t="n">
-        <v>1731</v>
+        <v>1985</v>
       </c>
       <c r="E196" s="9" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="197">
@@ -8731,10 +8737,10 @@
         </is>
       </c>
       <c r="D197" s="8" t="n">
-        <v>1023</v>
+        <v>1183</v>
       </c>
       <c r="E197" s="9" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="198">
@@ -8754,10 +8760,10 @@
         </is>
       </c>
       <c r="D198" s="8" t="n">
-        <v>679</v>
+        <v>755</v>
       </c>
       <c r="E198" s="9" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="199">
@@ -8777,10 +8783,10 @@
         </is>
       </c>
       <c r="D199" s="8" t="n">
-        <v>1795</v>
+        <v>2033</v>
       </c>
       <c r="E199" s="9" t="n">
-        <v>52.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="200">
@@ -8800,7 +8806,7 @@
         </is>
       </c>
       <c r="D200" s="8" t="n">
-        <v>1187</v>
+        <v>1359</v>
       </c>
       <c r="E200" s="9" t="n">
         <v>34.6</v>
@@ -8823,10 +8829,10 @@
         </is>
       </c>
       <c r="D201" s="8" t="n">
-        <v>451</v>
+        <v>531</v>
       </c>
       <c r="E201" s="9" t="n">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="202">
@@ -8846,10 +8852,10 @@
         </is>
       </c>
       <c r="D202" s="8" t="n">
-        <v>1386</v>
+        <v>1578</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="203">
@@ -8869,10 +8875,10 @@
         </is>
       </c>
       <c r="D203" s="8" t="n">
-        <v>1323</v>
+        <v>1494</v>
       </c>
       <c r="E203" s="9" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="204">
@@ -8892,10 +8898,10 @@
         </is>
       </c>
       <c r="D204" s="8" t="n">
-        <v>709</v>
+        <v>833</v>
       </c>
       <c r="E204" s="9" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="205">
@@ -8915,10 +8921,10 @@
         </is>
       </c>
       <c r="D205" s="8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E205" s="9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="206">
@@ -8938,10 +8944,10 @@
         </is>
       </c>
       <c r="D206" s="8" t="n">
-        <v>2740</v>
+        <v>3206</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>62</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="207">
@@ -8961,10 +8967,10 @@
         </is>
       </c>
       <c r="D207" s="8" t="n">
-        <v>1497</v>
+        <v>1803</v>
       </c>
       <c r="E207" s="9" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="208">
@@ -8984,10 +8990,10 @@
         </is>
       </c>
       <c r="D208" s="8" t="n">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="E208" s="9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="209">
@@ -9007,10 +9013,10 @@
         </is>
       </c>
       <c r="D209" s="8" t="n">
-        <v>4017</v>
+        <v>4752</v>
       </c>
       <c r="E209" s="9" t="n">
-        <v>90.90000000000001</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="210">
@@ -9030,7 +9036,7 @@
         </is>
       </c>
       <c r="D210" s="8" t="n">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="E210" s="9" t="n">
         <v>7.7</v>
@@ -9053,10 +9059,10 @@
         </is>
       </c>
       <c r="D211" s="8" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E211" s="9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -9076,10 +9082,10 @@
         </is>
       </c>
       <c r="D212" s="8" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E212" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="213">
@@ -9099,10 +9105,10 @@
         </is>
       </c>
       <c r="D213" s="8" t="n">
-        <v>2055</v>
+        <v>2407</v>
       </c>
       <c r="E213" s="9" t="n">
-        <v>46.5</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="214">
@@ -9122,10 +9128,10 @@
         </is>
       </c>
       <c r="D214" s="8" t="n">
-        <v>1691</v>
+        <v>2010</v>
       </c>
       <c r="E214" s="9" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="215">
@@ -9145,10 +9151,10 @@
         </is>
       </c>
       <c r="D215" s="8" t="n">
-        <v>673</v>
+        <v>822</v>
       </c>
       <c r="E215" s="9" t="n">
-        <v>15.2</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="216">
@@ -9168,10 +9174,10 @@
         </is>
       </c>
       <c r="D216" s="8" t="n">
-        <v>2425</v>
+        <v>2805</v>
       </c>
       <c r="E216" s="9" t="n">
-        <v>54.9</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="217">
@@ -9191,10 +9197,10 @@
         </is>
       </c>
       <c r="D217" s="8" t="n">
-        <v>1514</v>
+        <v>1845</v>
       </c>
       <c r="E217" s="9" t="n">
-        <v>34.3</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="218">
@@ -9214,10 +9220,10 @@
         </is>
       </c>
       <c r="D218" s="8" t="n">
-        <v>480</v>
+        <v>589</v>
       </c>
       <c r="E218" s="9" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="219">
@@ -9237,10 +9243,10 @@
         </is>
       </c>
       <c r="D219" s="8" t="n">
-        <v>1927</v>
+        <v>2272</v>
       </c>
       <c r="E219" s="9" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="220">
@@ -9260,10 +9266,10 @@
         </is>
       </c>
       <c r="D220" s="8" t="n">
-        <v>1682</v>
+        <v>1989</v>
       </c>
       <c r="E220" s="9" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="221">
@@ -9283,10 +9289,10 @@
         </is>
       </c>
       <c r="D221" s="8" t="n">
-        <v>800</v>
+        <v>964</v>
       </c>
       <c r="E221" s="9" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="222">
@@ -9306,10 +9312,10 @@
         </is>
       </c>
       <c r="D222" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E222" s="9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="223">
@@ -9329,10 +9335,10 @@
         </is>
       </c>
       <c r="D223" s="8" t="n">
-        <v>1711</v>
+        <v>1928</v>
       </c>
       <c r="E223" s="9" t="n">
-        <v>70.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="224">
@@ -9352,10 +9358,10 @@
         </is>
       </c>
       <c r="D224" s="8" t="n">
-        <v>642</v>
+        <v>743</v>
       </c>
       <c r="E224" s="9" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="225">
@@ -9375,7 +9381,7 @@
         </is>
       </c>
       <c r="D225" s="8" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E225" s="9" t="n">
         <v>3.4</v>
@@ -9398,10 +9404,10 @@
         </is>
       </c>
       <c r="D226" s="8" t="n">
-        <v>2099</v>
+        <v>2379</v>
       </c>
       <c r="E226" s="9" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="227">
@@ -9421,10 +9427,10 @@
         </is>
       </c>
       <c r="D227" s="8" t="n">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="E227" s="9" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="228">
@@ -9444,7 +9450,7 @@
         </is>
       </c>
       <c r="D228" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E228" s="9" t="n">
         <v>0.9</v>
@@ -9467,10 +9473,10 @@
         </is>
       </c>
       <c r="D229" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E229" s="9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="230">
@@ -9490,10 +9496,10 @@
         </is>
       </c>
       <c r="D230" s="8" t="n">
-        <v>1299</v>
+        <v>1469</v>
       </c>
       <c r="E230" s="9" t="n">
-        <v>53.3</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="231">
@@ -9513,10 +9519,10 @@
         </is>
       </c>
       <c r="D231" s="8" t="n">
-        <v>782</v>
+        <v>902</v>
       </c>
       <c r="E231" s="9" t="n">
-        <v>32.1</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="232">
@@ -9536,10 +9542,10 @@
         </is>
       </c>
       <c r="D232" s="8" t="n">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="E232" s="9" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="233">
@@ -9559,10 +9565,10 @@
         </is>
       </c>
       <c r="D233" s="8" t="n">
-        <v>1547</v>
+        <v>1732</v>
       </c>
       <c r="E233" s="9" t="n">
-        <v>63.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="234">
@@ -9582,10 +9588,10 @@
         </is>
       </c>
       <c r="D234" s="8" t="n">
-        <v>613</v>
+        <v>686</v>
       </c>
       <c r="E234" s="9" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="235">
@@ -9605,10 +9611,10 @@
         </is>
       </c>
       <c r="D235" s="8" t="n">
-        <v>276</v>
+        <v>347</v>
       </c>
       <c r="E235" s="9" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="236">
@@ -9628,10 +9634,10 @@
         </is>
       </c>
       <c r="D236" s="8" t="n">
-        <v>1051</v>
+        <v>1156</v>
       </c>
       <c r="E236" s="9" t="n">
-        <v>43.1</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="237">
@@ -9651,10 +9657,10 @@
         </is>
       </c>
       <c r="D237" s="8" t="n">
-        <v>872</v>
+        <v>992</v>
       </c>
       <c r="E237" s="9" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="238">
@@ -9674,10 +9680,10 @@
         </is>
       </c>
       <c r="D238" s="8" t="n">
-        <v>511</v>
+        <v>614</v>
       </c>
       <c r="E238" s="9" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="239">
@@ -9697,7 +9703,7 @@
         </is>
       </c>
       <c r="D239" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E239" s="9" t="n">
         <v>0.1</v>
@@ -9720,10 +9726,10 @@
         </is>
       </c>
       <c r="D240" s="8" t="n">
-        <v>14783</v>
+        <v>16994</v>
       </c>
       <c r="E240" s="9" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="241">
@@ -9743,10 +9749,10 @@
         </is>
       </c>
       <c r="D241" s="8" t="n">
-        <v>7323</v>
+        <v>8486</v>
       </c>
       <c r="E241" s="9" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="242">
@@ -9766,7 +9772,7 @@
         </is>
       </c>
       <c r="D242" s="8" t="n">
-        <v>1679</v>
+        <v>1944</v>
       </c>
       <c r="E242" s="9" t="n">
         <v>7.1</v>
@@ -9789,10 +9795,10 @@
         </is>
       </c>
       <c r="D243" s="8" t="n">
-        <v>20172</v>
+        <v>23233</v>
       </c>
       <c r="E243" s="9" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="244">
@@ -9812,7 +9818,7 @@
         </is>
       </c>
       <c r="D244" s="8" t="n">
-        <v>2749</v>
+        <v>3180</v>
       </c>
       <c r="E244" s="9" t="n">
         <v>11.6</v>
@@ -9835,7 +9841,7 @@
         </is>
       </c>
       <c r="D245" s="8" t="n">
-        <v>433</v>
+        <v>506</v>
       </c>
       <c r="E245" s="9" t="n">
         <v>1.8</v>
@@ -9858,7 +9864,7 @@
         </is>
       </c>
       <c r="D246" s="8" t="n">
-        <v>431</v>
+        <v>505</v>
       </c>
       <c r="E246" s="9" t="n">
         <v>1.8</v>
@@ -9881,7 +9887,7 @@
         </is>
       </c>
       <c r="D247" s="8" t="n">
-        <v>12829</v>
+        <v>14774</v>
       </c>
       <c r="E247" s="9" t="n">
         <v>53.9</v>
@@ -9904,10 +9910,10 @@
         </is>
       </c>
       <c r="D248" s="8" t="n">
-        <v>7432</v>
+        <v>8613</v>
       </c>
       <c r="E248" s="9" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="249">
@@ -9927,10 +9933,10 @@
         </is>
       </c>
       <c r="D249" s="8" t="n">
-        <v>3524</v>
+        <v>4037</v>
       </c>
       <c r="E249" s="9" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="250">
@@ -9950,10 +9956,10 @@
         </is>
       </c>
       <c r="D250" s="8" t="n">
-        <v>11469</v>
+        <v>13165</v>
       </c>
       <c r="E250" s="9" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="251">
@@ -9973,10 +9979,10 @@
         </is>
       </c>
       <c r="D251" s="8" t="n">
-        <v>8896</v>
+        <v>10297</v>
       </c>
       <c r="E251" s="9" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="252">
@@ -9996,7 +10002,7 @@
         </is>
       </c>
       <c r="D252" s="8" t="n">
-        <v>3420</v>
+        <v>3962</v>
       </c>
       <c r="E252" s="9" t="n">
         <v>14.4</v>
@@ -10019,7 +10025,7 @@
         </is>
       </c>
       <c r="D253" s="8" t="n">
-        <v>9731</v>
+        <v>11218</v>
       </c>
       <c r="E253" s="9" t="n">
         <v>40.9</v>
@@ -10042,7 +10048,7 @@
         </is>
       </c>
       <c r="D254" s="8" t="n">
-        <v>8395</v>
+        <v>9679</v>
       </c>
       <c r="E254" s="9" t="n">
         <v>35.3</v>
@@ -10065,7 +10071,7 @@
         </is>
       </c>
       <c r="D255" s="8" t="n">
-        <v>5564</v>
+        <v>6417</v>
       </c>
       <c r="E255" s="9" t="n">
         <v>23.4</v>
@@ -10088,7 +10094,7 @@
         </is>
       </c>
       <c r="D256" s="8" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E256" s="9" t="n">
         <v>0.4</v>
@@ -10111,10 +10117,10 @@
         </is>
       </c>
       <c r="D257" s="8" t="n">
-        <v>1015</v>
+        <v>1167</v>
       </c>
       <c r="E257" s="9" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="258">
@@ -10134,10 +10140,10 @@
         </is>
       </c>
       <c r="D258" s="8" t="n">
-        <v>563</v>
+        <v>665</v>
       </c>
       <c r="E258" s="9" t="n">
-        <v>34.6</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="259">
@@ -10157,10 +10163,10 @@
         </is>
       </c>
       <c r="D259" s="8" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E259" s="9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="260">
@@ -10180,7 +10186,7 @@
         </is>
       </c>
       <c r="D260" s="8" t="n">
-        <v>1487</v>
+        <v>1730</v>
       </c>
       <c r="E260" s="9" t="n">
         <v>91.3</v>
@@ -10203,10 +10209,10 @@
         </is>
       </c>
       <c r="D261" s="8" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="E261" s="9" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="262">
@@ -10226,7 +10232,7 @@
         </is>
       </c>
       <c r="D262" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E262" s="9" t="n">
         <v>0.7</v>
@@ -10249,10 +10255,10 @@
         </is>
       </c>
       <c r="D263" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E263" s="9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="264">
@@ -10272,10 +10278,10 @@
         </is>
       </c>
       <c r="D264" s="8" t="n">
-        <v>860</v>
+        <v>996</v>
       </c>
       <c r="E264" s="9" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="265">
@@ -10295,10 +10301,10 @@
         </is>
       </c>
       <c r="D265" s="8" t="n">
-        <v>610</v>
+        <v>714</v>
       </c>
       <c r="E265" s="9" t="n">
-        <v>37.4</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="266">
@@ -10318,10 +10324,10 @@
         </is>
       </c>
       <c r="D266" s="8" t="n">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="E266" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="267">
@@ -10341,10 +10347,10 @@
         </is>
       </c>
       <c r="D267" s="8" t="n">
-        <v>877</v>
+        <v>1003</v>
       </c>
       <c r="E267" s="9" t="n">
-        <v>53.8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="268">
@@ -10364,10 +10370,10 @@
         </is>
       </c>
       <c r="D268" s="8" t="n">
-        <v>485</v>
+        <v>578</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="269">
@@ -10387,10 +10393,10 @@
         </is>
       </c>
       <c r="D269" s="8" t="n">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="E269" s="9" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="270">
@@ -10410,10 +10416,10 @@
         </is>
       </c>
       <c r="D270" s="8" t="n">
-        <v>623</v>
+        <v>704</v>
       </c>
       <c r="E270" s="9" t="n">
-        <v>38.2</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="271">
@@ -10433,10 +10439,10 @@
         </is>
       </c>
       <c r="D271" s="8" t="n">
-        <v>567</v>
+        <v>664</v>
       </c>
       <c r="E271" s="9" t="n">
-        <v>34.8</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="272">
@@ -10456,10 +10462,10 @@
         </is>
       </c>
       <c r="D272" s="8" t="n">
-        <v>435</v>
+        <v>522</v>
       </c>
       <c r="E272" s="9" t="n">
-        <v>26.7</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="273">
@@ -10502,10 +10508,10 @@
         </is>
       </c>
       <c r="D274" s="8" t="n">
-        <v>470</v>
+        <v>532</v>
       </c>
       <c r="E274" s="9" t="n">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="275">
@@ -10525,10 +10531,10 @@
         </is>
       </c>
       <c r="D275" s="8" t="n">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="E275" s="9" t="n">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="276">
@@ -10548,10 +10554,10 @@
         </is>
       </c>
       <c r="D276" s="8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E276" s="9" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="277">
@@ -10571,10 +10577,10 @@
         </is>
       </c>
       <c r="D277" s="8" t="n">
-        <v>665</v>
+        <v>767</v>
       </c>
       <c r="E277" s="9" t="n">
-        <v>92</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="278">
@@ -10594,10 +10600,10 @@
         </is>
       </c>
       <c r="D278" s="8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E278" s="9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="279">
@@ -10620,7 +10626,7 @@
         <v>8</v>
       </c>
       <c r="E279" s="9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -10643,7 +10649,7 @@
         <v>2</v>
       </c>
       <c r="E280" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="281">
@@ -10663,7 +10669,7 @@
         </is>
       </c>
       <c r="D281" s="8" t="n">
-        <v>580</v>
+        <v>666</v>
       </c>
       <c r="E281" s="9" t="n">
         <v>80.2</v>
@@ -10686,10 +10692,10 @@
         </is>
       </c>
       <c r="D282" s="8" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E282" s="9" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="283">
@@ -10709,10 +10715,10 @@
         </is>
       </c>
       <c r="D283" s="8" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E283" s="9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="284">
@@ -10732,10 +10738,10 @@
         </is>
       </c>
       <c r="D284" s="8" t="n">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="E284" s="9" t="n">
-        <v>57.8</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="285">
@@ -10755,10 +10761,10 @@
         </is>
       </c>
       <c r="D285" s="8" t="n">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="E285" s="9" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="286">
@@ -10778,10 +10784,10 @@
         </is>
       </c>
       <c r="D286" s="8" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E286" s="9" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="287">
@@ -10801,10 +10807,10 @@
         </is>
       </c>
       <c r="D287" s="8" t="n">
-        <v>342</v>
+        <v>382</v>
       </c>
       <c r="E287" s="9" t="n">
-        <v>47.3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="288">
@@ -10824,10 +10830,10 @@
         </is>
       </c>
       <c r="D288" s="8" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="E288" s="9" t="n">
-        <v>30.3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="289">
@@ -10847,10 +10853,10 @@
         </is>
       </c>
       <c r="D289" s="8" t="n">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="E289" s="9" t="n">
-        <v>22.1</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="290">
@@ -10873,7 +10879,7 @@
         <v>2</v>
       </c>
       <c r="E290" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="291">
@@ -10893,10 +10899,10 @@
         </is>
       </c>
       <c r="D291" s="8" t="n">
-        <v>585</v>
+        <v>654</v>
       </c>
       <c r="E291" s="9" t="n">
-        <v>69.8</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="292">
@@ -10916,10 +10922,10 @@
         </is>
       </c>
       <c r="D292" s="8" t="n">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="E292" s="9" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="293">
@@ -10939,10 +10945,10 @@
         </is>
       </c>
       <c r="D293" s="8" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E293" s="9" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="294">
@@ -10962,10 +10968,10 @@
         </is>
       </c>
       <c r="D294" s="8" t="n">
-        <v>677</v>
+        <v>769</v>
       </c>
       <c r="E294" s="9" t="n">
-        <v>80.8</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -10985,7 +10991,7 @@
         </is>
       </c>
       <c r="D295" s="8" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="E295" s="9" t="n">
         <v>15.2</v>
@@ -11004,14 +11010,14 @@
       </c>
       <c r="C296" s="7" t="inlineStr">
         <is>
-          <t>Viudo/a</t>
+          <t>Divorciado/a</t>
         </is>
       </c>
       <c r="D296" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E296" s="9" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="297">
@@ -11027,14 +11033,14 @@
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>Divorciado/a</t>
+          <t>Viudo/a</t>
         </is>
       </c>
       <c r="D297" s="8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E297" s="9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="298">
@@ -11054,10 +11060,10 @@
         </is>
       </c>
       <c r="D298" s="8" t="n">
-        <v>414</v>
+        <v>464</v>
       </c>
       <c r="E298" s="9" t="n">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="299">
@@ -11077,10 +11083,10 @@
         </is>
       </c>
       <c r="D299" s="8" t="n">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E299" s="9" t="n">
-        <v>29</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="300">
@@ -11100,10 +11106,10 @@
         </is>
       </c>
       <c r="D300" s="8" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="E300" s="9" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="301">
@@ -11123,10 +11129,10 @@
         </is>
       </c>
       <c r="D301" s="8" t="n">
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="E301" s="9" t="n">
-        <v>57.6</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="302">
@@ -11146,10 +11152,10 @@
         </is>
       </c>
       <c r="D302" s="8" t="n">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="E302" s="9" t="n">
-        <v>31.7</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="303">
@@ -11169,10 +11175,10 @@
         </is>
       </c>
       <c r="D303" s="8" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E303" s="9" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="304">
@@ -11192,10 +11198,10 @@
         </is>
       </c>
       <c r="D304" s="8" t="n">
-        <v>390</v>
+        <v>436</v>
       </c>
       <c r="E304" s="9" t="n">
-        <v>46.5</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="305">
@@ -11215,10 +11221,10 @@
         </is>
       </c>
       <c r="D305" s="8" t="n">
-        <v>331</v>
+        <v>377</v>
       </c>
       <c r="E305" s="9" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="306">
@@ -11238,10 +11244,10 @@
         </is>
       </c>
       <c r="D306" s="8" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="E306" s="9" t="n">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="307">
@@ -11261,7 +11267,7 @@
         </is>
       </c>
       <c r="D307" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E307" s="9" t="n">
         <v>0.4</v>
@@ -11284,10 +11290,10 @@
         </is>
       </c>
       <c r="D308" s="8" t="n">
-        <v>491</v>
+        <v>576</v>
       </c>
       <c r="E308" s="9" t="n">
-        <v>69.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="309">
@@ -11307,10 +11313,10 @@
         </is>
       </c>
       <c r="D309" s="8" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="E309" s="9" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="310">
@@ -11330,10 +11336,10 @@
         </is>
       </c>
       <c r="D310" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E310" s="9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="311">
@@ -11353,10 +11359,10 @@
         </is>
       </c>
       <c r="D311" s="8" t="n">
-        <v>637</v>
+        <v>746</v>
       </c>
       <c r="E311" s="9" t="n">
-        <v>89.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="312">
@@ -11376,10 +11382,10 @@
         </is>
       </c>
       <c r="D312" s="8" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E312" s="9" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="313">
@@ -11399,10 +11405,10 @@
         </is>
       </c>
       <c r="D313" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E313" s="9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="314">
@@ -11425,7 +11431,7 @@
         <v>2</v>
       </c>
       <c r="E314" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="315">
@@ -11445,10 +11451,10 @@
         </is>
       </c>
       <c r="D315" s="8" t="n">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="E315" s="9" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="316">
@@ -11468,10 +11474,10 @@
         </is>
       </c>
       <c r="D316" s="8" t="n">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="E316" s="9" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="317">
@@ -11491,10 +11497,10 @@
         </is>
       </c>
       <c r="D317" s="8" t="n">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="E317" s="9" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="318">
@@ -11514,10 +11520,10 @@
         </is>
       </c>
       <c r="D318" s="8" t="n">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="E318" s="9" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="319">
@@ -11537,10 +11543,10 @@
         </is>
       </c>
       <c r="D319" s="8" t="n">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="E319" s="9" t="n">
-        <v>33.8</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="320">
@@ -11560,10 +11566,10 @@
         </is>
       </c>
       <c r="D320" s="8" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E320" s="9" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="321">
@@ -11579,14 +11585,14 @@
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>Psicológica</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="D321" s="8" t="n">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="E321" s="9" t="n">
-        <v>41.1</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="322">
@@ -11602,14 +11608,14 @@
       </c>
       <c r="C322" s="7" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Psicológica</t>
         </is>
       </c>
       <c r="D322" s="8" t="n">
-        <v>291</v>
+        <v>338</v>
       </c>
       <c r="E322" s="9" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="323">
@@ -11629,10 +11635,10 @@
         </is>
       </c>
       <c r="D323" s="8" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E323" s="9" t="n">
-        <v>17.6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="324">
@@ -11675,10 +11681,10 @@
         </is>
       </c>
       <c r="D325" s="8" t="n">
-        <v>2960</v>
+        <v>3400</v>
       </c>
       <c r="E325" s="9" t="n">
-        <v>73.7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="326">
@@ -11698,10 +11704,10 @@
         </is>
       </c>
       <c r="D326" s="8" t="n">
-        <v>889</v>
+        <v>1050</v>
       </c>
       <c r="E326" s="9" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="327">
@@ -11721,10 +11727,10 @@
         </is>
       </c>
       <c r="D327" s="8" t="n">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="E327" s="9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="328">
@@ -11744,10 +11750,10 @@
         </is>
       </c>
       <c r="D328" s="8" t="n">
-        <v>3409</v>
+        <v>3967</v>
       </c>
       <c r="E328" s="9" t="n">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="329">
@@ -11767,10 +11773,10 @@
         </is>
       </c>
       <c r="D329" s="8" t="n">
-        <v>554</v>
+        <v>617</v>
       </c>
       <c r="E329" s="9" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="330">
@@ -11790,10 +11796,10 @@
         </is>
       </c>
       <c r="D330" s="8" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E330" s="9" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="331">
@@ -11813,7 +11819,7 @@
         </is>
       </c>
       <c r="D331" s="8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E331" s="9" t="n">
         <v>0.6</v>
@@ -11836,10 +11842,10 @@
         </is>
       </c>
       <c r="D332" s="8" t="n">
-        <v>2049</v>
+        <v>2332</v>
       </c>
       <c r="E332" s="9" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="333">
@@ -11859,10 +11865,10 @@
         </is>
       </c>
       <c r="D333" s="8" t="n">
-        <v>1043</v>
+        <v>1233</v>
       </c>
       <c r="E333" s="9" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="334">
@@ -11882,10 +11888,10 @@
         </is>
       </c>
       <c r="D334" s="8" t="n">
-        <v>923</v>
+        <v>1092</v>
       </c>
       <c r="E334" s="9" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="335">
@@ -11905,10 +11911,10 @@
         </is>
       </c>
       <c r="D335" s="8" t="n">
-        <v>2534</v>
+        <v>2909</v>
       </c>
       <c r="E335" s="9" t="n">
-        <v>63.1</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="336">
@@ -11928,10 +11934,10 @@
         </is>
       </c>
       <c r="D336" s="8" t="n">
-        <v>1101</v>
+        <v>1294</v>
       </c>
       <c r="E336" s="9" t="n">
-        <v>27.4</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="337">
@@ -11951,10 +11957,10 @@
         </is>
       </c>
       <c r="D337" s="8" t="n">
-        <v>380</v>
+        <v>454</v>
       </c>
       <c r="E337" s="9" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="338">
@@ -11974,10 +11980,10 @@
         </is>
       </c>
       <c r="D338" s="8" t="n">
-        <v>1805</v>
+        <v>2065</v>
       </c>
       <c r="E338" s="9" t="n">
-        <v>45</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="339">
@@ -11997,7 +12003,7 @@
         </is>
       </c>
       <c r="D339" s="8" t="n">
-        <v>1606</v>
+        <v>1865</v>
       </c>
       <c r="E339" s="9" t="n">
         <v>40</v>
@@ -12020,10 +12026,10 @@
         </is>
       </c>
       <c r="D340" s="8" t="n">
-        <v>600</v>
+        <v>713</v>
       </c>
       <c r="E340" s="9" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="341">
@@ -12043,10 +12049,10 @@
         </is>
       </c>
       <c r="D341" s="8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E341" s="9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="342">
@@ -12066,10 +12072,10 @@
         </is>
       </c>
       <c r="D342" s="8" t="n">
-        <v>1709</v>
+        <v>1950</v>
       </c>
       <c r="E342" s="9" t="n">
-        <v>71.5</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="343">
@@ -12089,10 +12095,10 @@
         </is>
       </c>
       <c r="D343" s="8" t="n">
-        <v>487</v>
+        <v>565</v>
       </c>
       <c r="E343" s="9" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="344">
@@ -12112,10 +12118,10 @@
         </is>
       </c>
       <c r="D344" s="8" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="E344" s="9" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="345">
@@ -12135,10 +12141,10 @@
         </is>
       </c>
       <c r="D345" s="8" t="n">
-        <v>1880</v>
+        <v>2152</v>
       </c>
       <c r="E345" s="9" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="346">
@@ -12158,7 +12164,7 @@
         </is>
       </c>
       <c r="D346" s="8" t="n">
-        <v>418</v>
+        <v>480</v>
       </c>
       <c r="E346" s="9" t="n">
         <v>17.5</v>
@@ -12181,10 +12187,10 @@
         </is>
       </c>
       <c r="D347" s="8" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E347" s="9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="348">
@@ -12204,10 +12210,10 @@
         </is>
       </c>
       <c r="D348" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E348" s="9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="349">
@@ -12227,10 +12233,10 @@
         </is>
       </c>
       <c r="D349" s="8" t="n">
-        <v>1359</v>
+        <v>1562</v>
       </c>
       <c r="E349" s="9" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="350">
@@ -12250,10 +12256,10 @@
         </is>
       </c>
       <c r="D350" s="8" t="n">
-        <v>534</v>
+        <v>613</v>
       </c>
       <c r="E350" s="9" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="351">
@@ -12273,10 +12279,10 @@
         </is>
       </c>
       <c r="D351" s="8" t="n">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="E351" s="9" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="352">
@@ -12296,10 +12302,10 @@
         </is>
       </c>
       <c r="D352" s="8" t="n">
-        <v>1313</v>
+        <v>1496</v>
       </c>
       <c r="E352" s="9" t="n">
-        <v>54.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="353">
@@ -12319,10 +12325,10 @@
         </is>
       </c>
       <c r="D353" s="8" t="n">
-        <v>847</v>
+        <v>973</v>
       </c>
       <c r="E353" s="9" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="354">
@@ -12342,10 +12348,10 @@
         </is>
       </c>
       <c r="D354" s="8" t="n">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="E354" s="9" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="355">
@@ -12365,10 +12371,10 @@
         </is>
       </c>
       <c r="D355" s="8" t="n">
-        <v>1145</v>
+        <v>1293</v>
       </c>
       <c r="E355" s="9" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="356">
@@ -12388,10 +12394,10 @@
         </is>
       </c>
       <c r="D356" s="8" t="n">
-        <v>906</v>
+        <v>1044</v>
       </c>
       <c r="E356" s="9" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="357">
@@ -12411,10 +12417,10 @@
         </is>
       </c>
       <c r="D357" s="8" t="n">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="E357" s="9" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="358">
@@ -12434,7 +12440,7 @@
         </is>
       </c>
       <c r="D358" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E358" s="9" t="n">
         <v>0.5</v>
@@ -12457,10 +12463,10 @@
         </is>
       </c>
       <c r="D359" s="8" t="n">
-        <v>2104</v>
+        <v>2426</v>
       </c>
       <c r="E359" s="9" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="360">
@@ -12480,10 +12486,10 @@
         </is>
       </c>
       <c r="D360" s="8" t="n">
-        <v>1074</v>
+        <v>1247</v>
       </c>
       <c r="E360" s="9" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="361">
@@ -12503,10 +12509,10 @@
         </is>
       </c>
       <c r="D361" s="8" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E361" s="9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="362">
@@ -12526,10 +12532,10 @@
         </is>
       </c>
       <c r="D362" s="8" t="n">
-        <v>3003</v>
+        <v>3470</v>
       </c>
       <c r="E362" s="9" t="n">
-        <v>90.8</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="363">
@@ -12549,7 +12555,7 @@
         </is>
       </c>
       <c r="D363" s="8" t="n">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="E363" s="9" t="n">
         <v>7.6</v>
@@ -12572,10 +12578,10 @@
         </is>
       </c>
       <c r="D364" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E364" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="365">
@@ -12595,10 +12601,10 @@
         </is>
       </c>
       <c r="D365" s="8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E365" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="366">
@@ -12618,10 +12624,10 @@
         </is>
       </c>
       <c r="D366" s="8" t="n">
-        <v>1647</v>
+        <v>1921</v>
       </c>
       <c r="E366" s="9" t="n">
-        <v>49.8</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="367">
@@ -12641,10 +12647,10 @@
         </is>
       </c>
       <c r="D367" s="8" t="n">
-        <v>1074</v>
+        <v>1224</v>
       </c>
       <c r="E367" s="9" t="n">
-        <v>32.5</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="368">
@@ -12664,10 +12670,10 @@
         </is>
       </c>
       <c r="D368" s="8" t="n">
-        <v>585</v>
+        <v>673</v>
       </c>
       <c r="E368" s="9" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="369">
@@ -12687,10 +12693,10 @@
         </is>
       </c>
       <c r="D369" s="8" t="n">
-        <v>1808</v>
+        <v>2078</v>
       </c>
       <c r="E369" s="9" t="n">
-        <v>54.7</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="370">
@@ -12710,10 +12716,10 @@
         </is>
       </c>
       <c r="D370" s="8" t="n">
-        <v>1001</v>
+        <v>1182</v>
       </c>
       <c r="E370" s="9" t="n">
-        <v>30.3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="371">
@@ -12733,10 +12739,10 @@
         </is>
       </c>
       <c r="D371" s="8" t="n">
-        <v>497</v>
+        <v>558</v>
       </c>
       <c r="E371" s="9" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="372">
@@ -12756,10 +12762,10 @@
         </is>
       </c>
       <c r="D372" s="8" t="n">
-        <v>1379</v>
+        <v>1582</v>
       </c>
       <c r="E372" s="9" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="373">
@@ -12779,10 +12785,10 @@
         </is>
       </c>
       <c r="D373" s="8" t="n">
-        <v>1123</v>
+        <v>1305</v>
       </c>
       <c r="E373" s="9" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="374">
@@ -12802,10 +12808,10 @@
         </is>
       </c>
       <c r="D374" s="8" t="n">
-        <v>797</v>
+        <v>923</v>
       </c>
       <c r="E374" s="9" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="375">
@@ -12825,7 +12831,7 @@
         </is>
       </c>
       <c r="D375" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E375" s="9" t="n">
         <v>0.2</v>
@@ -12848,10 +12854,10 @@
         </is>
       </c>
       <c r="D376" s="8" t="n">
-        <v>1080</v>
+        <v>1219</v>
       </c>
       <c r="E376" s="9" t="n">
-        <v>66.09999999999999</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="377">
@@ -12871,10 +12877,10 @@
         </is>
       </c>
       <c r="D377" s="8" t="n">
-        <v>478</v>
+        <v>535</v>
       </c>
       <c r="E377" s="9" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="378">
@@ -12894,7 +12900,7 @@
         </is>
       </c>
       <c r="D378" s="8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E378" s="9" t="n">
         <v>4.6</v>
@@ -12917,10 +12923,10 @@
         </is>
       </c>
       <c r="D379" s="8" t="n">
-        <v>1423</v>
+        <v>1607</v>
       </c>
       <c r="E379" s="9" t="n">
-        <v>87.09999999999999</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="380">
@@ -12940,10 +12946,10 @@
         </is>
       </c>
       <c r="D380" s="8" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="E380" s="9" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="381">
@@ -12963,10 +12969,10 @@
         </is>
       </c>
       <c r="D381" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E381" s="9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="382">
@@ -12986,10 +12992,10 @@
         </is>
       </c>
       <c r="D382" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E382" s="9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="383">
@@ -13009,10 +13015,10 @@
         </is>
       </c>
       <c r="D383" s="8" t="n">
-        <v>869</v>
+        <v>984</v>
       </c>
       <c r="E383" s="9" t="n">
-        <v>53.2</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="384">
@@ -13032,10 +13038,10 @@
         </is>
       </c>
       <c r="D384" s="8" t="n">
-        <v>599</v>
+        <v>665</v>
       </c>
       <c r="E384" s="9" t="n">
-        <v>36.7</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="385">
@@ -13055,10 +13061,10 @@
         </is>
       </c>
       <c r="D385" s="8" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E385" s="9" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="386">
@@ -13078,10 +13084,10 @@
         </is>
       </c>
       <c r="D386" s="8" t="n">
-        <v>814</v>
+        <v>927</v>
       </c>
       <c r="E386" s="9" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="387">
@@ -13101,10 +13107,10 @@
         </is>
       </c>
       <c r="D387" s="8" t="n">
-        <v>601</v>
+        <v>671</v>
       </c>
       <c r="E387" s="9" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="388">
@@ -13124,10 +13130,10 @@
         </is>
       </c>
       <c r="D388" s="8" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="E388" s="9" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="389">
@@ -13147,10 +13153,10 @@
         </is>
       </c>
       <c r="D389" s="8" t="n">
-        <v>675</v>
+        <v>767</v>
       </c>
       <c r="E389" s="9" t="n">
-        <v>41.3</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="390">
@@ -13170,10 +13176,10 @@
         </is>
       </c>
       <c r="D390" s="8" t="n">
-        <v>638</v>
+        <v>714</v>
       </c>
       <c r="E390" s="9" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="391">
@@ -13193,10 +13199,10 @@
         </is>
       </c>
       <c r="D391" s="8" t="n">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="392">
@@ -13239,7 +13245,7 @@
         </is>
       </c>
       <c r="D393" s="8" t="n">
-        <v>755</v>
+        <v>862</v>
       </c>
       <c r="E393" s="9" t="n">
         <v>70.8</v>
@@ -13262,10 +13268,10 @@
         </is>
       </c>
       <c r="D394" s="8" t="n">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="E394" s="9" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="395">
@@ -13285,10 +13291,10 @@
         </is>
       </c>
       <c r="D395" s="8" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="396">
@@ -13308,10 +13314,10 @@
         </is>
       </c>
       <c r="D396" s="8" t="n">
-        <v>936</v>
+        <v>1067</v>
       </c>
       <c r="E396" s="9" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="397">
@@ -13331,7 +13337,7 @@
         </is>
       </c>
       <c r="D397" s="8" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E397" s="9" t="n">
         <v>10.7</v>
@@ -13354,10 +13360,10 @@
         </is>
       </c>
       <c r="D398" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E398" s="9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="399">
@@ -13377,10 +13383,10 @@
         </is>
       </c>
       <c r="D399" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="400">
@@ -13400,10 +13406,10 @@
         </is>
       </c>
       <c r="D400" s="8" t="n">
-        <v>578</v>
+        <v>652</v>
       </c>
       <c r="E400" s="9" t="n">
-        <v>54.2</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="401">
@@ -13423,10 +13429,10 @@
         </is>
       </c>
       <c r="D401" s="8" t="n">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>36.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="402">
@@ -13446,10 +13452,10 @@
         </is>
       </c>
       <c r="D402" s="8" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="E402" s="9" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="403">
@@ -13469,10 +13475,10 @@
         </is>
       </c>
       <c r="D403" s="8" t="n">
-        <v>695</v>
+        <v>795</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="404">
@@ -13492,7 +13498,7 @@
         </is>
       </c>
       <c r="D404" s="8" t="n">
-        <v>281</v>
+        <v>321</v>
       </c>
       <c r="E404" s="9" t="n">
         <v>26.4</v>
@@ -13515,10 +13521,10 @@
         </is>
       </c>
       <c r="D405" s="8" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="406">
@@ -13538,10 +13544,10 @@
         </is>
       </c>
       <c r="D406" s="8" t="n">
-        <v>482</v>
+        <v>547</v>
       </c>
       <c r="E406" s="9" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="407">
@@ -13561,10 +13567,10 @@
         </is>
       </c>
       <c r="D407" s="8" t="n">
-        <v>450</v>
+        <v>516</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="408">
@@ -13584,10 +13590,10 @@
         </is>
       </c>
       <c r="D408" s="8" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="E408" s="9" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="409">
@@ -13630,10 +13636,10 @@
         </is>
       </c>
       <c r="D410" s="8" t="n">
-        <v>788</v>
+        <v>914</v>
       </c>
       <c r="E410" s="9" t="n">
-        <v>55.9</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="411">
@@ -13653,10 +13659,10 @@
         </is>
       </c>
       <c r="D411" s="8" t="n">
-        <v>592</v>
+        <v>680</v>
       </c>
       <c r="E411" s="9" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="412">
@@ -13676,7 +13682,7 @@
         </is>
       </c>
       <c r="D412" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E412" s="9" t="n">
         <v>2.1</v>
@@ -13699,10 +13705,10 @@
         </is>
       </c>
       <c r="D413" s="8" t="n">
-        <v>1331</v>
+        <v>1535</v>
       </c>
       <c r="E413" s="9" t="n">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="414">
@@ -13722,10 +13728,10 @@
         </is>
       </c>
       <c r="D414" s="8" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E414" s="9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="415">
@@ -13745,7 +13751,7 @@
         </is>
       </c>
       <c r="D415" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E415" s="9" t="n">
         <v>0.4</v>
@@ -13791,10 +13797,10 @@
         </is>
       </c>
       <c r="D417" s="8" t="n">
-        <v>674</v>
+        <v>784</v>
       </c>
       <c r="E417" s="9" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="418">
@@ -13814,10 +13820,10 @@
         </is>
       </c>
       <c r="D418" s="8" t="n">
-        <v>555</v>
+        <v>635</v>
       </c>
       <c r="E418" s="9" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="419">
@@ -13837,10 +13843,10 @@
         </is>
       </c>
       <c r="D419" s="8" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="E419" s="9" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="420">
@@ -13860,10 +13866,10 @@
         </is>
       </c>
       <c r="D420" s="8" t="n">
-        <v>669</v>
+        <v>782</v>
       </c>
       <c r="E420" s="9" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="421">
@@ -13883,10 +13889,10 @@
         </is>
       </c>
       <c r="D421" s="8" t="n">
-        <v>459</v>
+        <v>520</v>
       </c>
       <c r="E421" s="9" t="n">
-        <v>32.6</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="422">
@@ -13906,10 +13912,10 @@
         </is>
       </c>
       <c r="D422" s="8" t="n">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="E422" s="9" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="423">
@@ -13925,14 +13931,14 @@
       </c>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Sexual</t>
         </is>
       </c>
       <c r="D423" s="8" t="n">
-        <v>491</v>
+        <v>565</v>
       </c>
       <c r="E423" s="9" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="424">
@@ -13948,14 +13954,14 @@
       </c>
       <c r="C424" s="7" t="inlineStr">
         <is>
-          <t>Sexual</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="D424" s="8" t="n">
-        <v>491</v>
+        <v>558</v>
       </c>
       <c r="E424" s="9" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="425">
@@ -13975,10 +13981,10 @@
         </is>
       </c>
       <c r="D425" s="8" t="n">
-        <v>424</v>
+        <v>501</v>
       </c>
       <c r="E425" s="9" t="n">
-        <v>30.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="426">
@@ -13998,7 +14004,7 @@
         </is>
       </c>
       <c r="D426" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E426" s="9" t="n">
         <v>0.3</v>
